--- a/InputData/trans/BNoEVC/BAU Number of EV Chargers.xlsx
+++ b/InputData/trans/BNoEVC/BAU Number of EV Chargers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\BRAaCTSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\United States\us-eps\InputData\trans\BNoEVC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EAF56AC-016E-492C-8470-28F213A73717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9BD963-EEEA-4715-A375-AFAFA333D411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="520" windowWidth="19180" windowHeight="10180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -652,10 +652,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="31.85546875" customWidth="1"/>
+    <col min="1" max="1" width="16.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.86328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -781,9 +781,9 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
-    <col min="1" max="1" width="29.140625" customWidth="1"/>
+    <col min="1" max="1" width="29.1328125" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -805,7 +805,7 @@
         <v>7500000000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30">
+    <row r="5" spans="1:2" ht="29.5">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -823,7 +823,7 @@
         <v>7943476215.0791588</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30">
+    <row r="8" spans="1:2" ht="29.5">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
@@ -831,7 +831,7 @@
         <v>24443</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30">
+    <row r="10" spans="1:2" ht="29.5">
       <c r="A10" s="7" t="s">
         <v>43</v>
       </c>
@@ -851,16 +851,16 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AL24"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="60.7109375" style="10" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" style="10" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" style="10" customWidth="1"/>
-    <col min="5" max="6" width="16.140625" style="10" customWidth="1"/>
-    <col min="7" max="11" width="12.5703125" style="10"/>
-    <col min="12" max="12" width="16.42578125" style="10" customWidth="1"/>
-    <col min="13" max="16384" width="12.5703125" style="10"/>
+    <col min="1" max="1" width="60.7265625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="27.40625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="17.86328125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="18.1328125" style="10" customWidth="1"/>
+    <col min="5" max="6" width="16.1328125" style="10" customWidth="1"/>
+    <col min="7" max="11" width="12.54296875" style="10"/>
+    <col min="12" max="12" width="16.40625" style="10" customWidth="1"/>
+    <col min="13" max="16384" width="12.54296875" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="14.25" customHeight="1">
@@ -905,7 +905,7 @@
       <c r="AK1" s="9"/>
       <c r="AL1" s="9"/>
     </row>
-    <row r="2" spans="1:38" ht="180">
+    <row r="2" spans="1:38" ht="162.25">
       <c r="A2" s="11" t="s">
         <v>23</v>
       </c>
@@ -1085,7 +1085,7 @@
       <c r="AK6" s="9"/>
       <c r="AL6" s="9"/>
     </row>
-    <row r="7" spans="1:38" ht="15">
+    <row r="7" spans="1:38" ht="14.75">
       <c r="A7" s="15" t="s">
         <v>25</v>
       </c>
@@ -1103,7 +1103,7 @@
       <c r="K7" s="12"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="1:38" ht="15">
+    <row r="8" spans="1:38" ht="14.75">
       <c r="A8" s="15" t="s">
         <v>26</v>
       </c>
@@ -1121,7 +1121,7 @@
       <c r="K8" s="12"/>
       <c r="L8" s="12"/>
     </row>
-    <row r="9" spans="1:38" ht="15">
+    <row r="9" spans="1:38" ht="14.75">
       <c r="A9" s="12"/>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
@@ -1135,7 +1135,7 @@
       <c r="K9" s="12"/>
       <c r="L9" s="12"/>
     </row>
-    <row r="10" spans="1:38" ht="15">
+    <row r="10" spans="1:38" ht="14.75">
       <c r="A10" s="17" t="s">
         <v>19</v>
       </c>
@@ -1179,7 +1179,7 @@
       <c r="AK10" s="16"/>
       <c r="AL10" s="16"/>
     </row>
-    <row r="11" spans="1:38" ht="15">
+    <row r="11" spans="1:38" ht="14.75">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -1219,7 +1219,7 @@
       <c r="AK11" s="16"/>
       <c r="AL11" s="16"/>
     </row>
-    <row r="12" spans="1:38" ht="30">
+    <row r="12" spans="1:38" ht="14.75">
       <c r="A12" s="17" t="s">
         <v>20</v>
       </c>
@@ -1263,7 +1263,7 @@
       <c r="AK12" s="16"/>
       <c r="AL12" s="16"/>
     </row>
-    <row r="13" spans="1:38" ht="15">
+    <row r="13" spans="1:38" ht="14.75">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -1303,7 +1303,7 @@
       <c r="AK13" s="16"/>
       <c r="AL13" s="16"/>
     </row>
-    <row r="14" spans="1:38" ht="15">
+    <row r="14" spans="1:38" ht="14.75">
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -1342,7 +1342,7 @@
       <c r="AK14" s="16"/>
       <c r="AL14" s="16"/>
     </row>
-    <row r="15" spans="1:38" ht="15">
+    <row r="15" spans="1:38" ht="14.75">
       <c r="A15" s="15"/>
       <c r="B15" s="12">
         <v>2022</v>
@@ -1404,7 +1404,7 @@
       <c r="AK15" s="16"/>
       <c r="AL15" s="16"/>
     </row>
-    <row r="16" spans="1:38" ht="15">
+    <row r="16" spans="1:38" ht="14.75">
       <c r="A16" s="15" t="s">
         <v>27</v>
       </c>
@@ -1464,7 +1464,7 @@
       <c r="AK16" s="16"/>
       <c r="AL16" s="16"/>
     </row>
-    <row r="17" spans="1:38" ht="15">
+    <row r="17" spans="1:38" ht="14.75">
       <c r="A17" s="12"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -1504,7 +1504,7 @@
       <c r="AK17" s="16"/>
       <c r="AL17" s="16"/>
     </row>
-    <row r="18" spans="1:38" ht="15">
+    <row r="18" spans="1:38" ht="14.75">
       <c r="A18" s="15" t="s">
         <v>31</v>
       </c>
@@ -1575,7 +1575,7 @@
       <c r="AK18" s="16"/>
       <c r="AL18" s="16"/>
     </row>
-    <row r="19" spans="1:38" ht="15">
+    <row r="19" spans="1:38" ht="14.75">
       <c r="A19" s="15"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
@@ -1615,7 +1615,7 @@
       <c r="AK19" s="16"/>
       <c r="AL19" s="16"/>
     </row>
-    <row r="20" spans="1:38" ht="15">
+    <row r="20" spans="1:38" ht="14.75">
       <c r="B20" s="12">
         <v>2022</v>
       </c>
@@ -1676,7 +1676,7 @@
       <c r="AK20" s="16"/>
       <c r="AL20" s="16"/>
     </row>
-    <row r="21" spans="1:38" ht="15">
+    <row r="21" spans="1:38" ht="14.75">
       <c r="A21" s="15" t="s">
         <v>21</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:38" ht="15">
+    <row r="22" spans="1:38" ht="14.75">
       <c r="A22" s="15"/>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -1764,7 +1764,7 @@
       <c r="AK22" s="16"/>
       <c r="AL22" s="16"/>
     </row>
-    <row r="23" spans="1:38" ht="15">
+    <row r="23" spans="1:38" ht="14.75">
       <c r="A23" s="15" t="s">
         <v>22</v>
       </c>
@@ -1783,7 +1783,7 @@
       <c r="K23" s="12"/>
       <c r="L23" s="12"/>
     </row>
-    <row r="24" spans="1:38" ht="15">
+    <row r="24" spans="1:38" ht="14.75">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -1834,10 +1834,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{341A17B3-AFD9-42DA-AB68-E46FC6CF1D40}">
   <dimension ref="A1:AF11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
-    <col min="1" max="1" width="45.140625" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" customWidth="1"/>
+    <col min="1" max="1" width="45.1328125" customWidth="1"/>
+    <col min="2" max="2" width="26.40625" customWidth="1"/>
     <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2206,41 +2206,32 @@
       <c r="D10">
         <v>0</v>
       </c>
-      <c r="E10" s="2">
-        <f>'Inflation Reduction Act'!C21</f>
-        <v>10932.127807552264</v>
-      </c>
-      <c r="F10" s="2">
-        <f>'Inflation Reduction Act'!D21</f>
-        <v>10139.944633091956</v>
-      </c>
-      <c r="G10" s="2">
-        <f>'Inflation Reduction Act'!E21</f>
-        <v>11486.656029674483</v>
-      </c>
-      <c r="H10" s="2">
-        <f>'Inflation Reduction Act'!F21</f>
-        <v>12991.804061149072</v>
-      </c>
-      <c r="I10" s="2">
-        <f>'Inflation Reduction Act'!G21</f>
-        <v>14576.17041006969</v>
-      </c>
-      <c r="J10" s="2">
-        <f>'Inflation Reduction Act'!H21</f>
-        <v>16398.1917113284</v>
-      </c>
-      <c r="K10" s="2">
-        <f>'Inflation Reduction Act'!I21</f>
-        <v>18299.431330033138</v>
-      </c>
-      <c r="L10" s="2">
-        <f>'Inflation Reduction Act'!J21</f>
-        <v>20359.107583629942</v>
-      </c>
-      <c r="M10" s="2">
-        <f>'Inflation Reduction Act'!K21</f>
-        <v>22498.00215467278</v>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -2318,115 +2309,115 @@
       </c>
       <c r="E11">
         <f t="shared" ref="E11:AF11" si="0">D11+(E8-D8)+SUM(E9:E10)</f>
-        <v>251762.11802742296</v>
+        <v>240829.9902198707</v>
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>364830.05288038554</v>
+        <v>343757.9804397414</v>
       </c>
       <c r="G11">
         <f t="shared" si="0"/>
-        <v>479244.6991299307</v>
+        <v>446685.9706596121</v>
       </c>
       <c r="H11">
         <f t="shared" si="0"/>
-        <v>595164.49341096531</v>
+        <v>549613.9608794977</v>
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>647672.73524960212</v>
+        <v>587546.03230806487</v>
       </c>
       <c r="J11">
         <f t="shared" si="0"/>
-        <v>702002.99838949763</v>
+        <v>625478.10373663204</v>
       </c>
       <c r="K11">
         <f t="shared" si="0"/>
-        <v>758234.50114811282</v>
+        <v>663410.17516521411</v>
       </c>
       <c r="L11">
         <f t="shared" si="0"/>
-        <v>816525.68016030989</v>
+        <v>701342.24659378128</v>
       </c>
       <c r="M11">
         <f t="shared" si="0"/>
-        <v>876955.75374354981</v>
+        <v>739274.31802234845</v>
       </c>
       <c r="N11">
         <f t="shared" si="0"/>
-        <v>914887.82517211698</v>
+        <v>777206.38945091562</v>
       </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>952819.89660069905</v>
+        <v>815138.4608794977</v>
       </c>
       <c r="P11">
         <f t="shared" si="0"/>
-        <v>990751.96802926622</v>
+        <v>853070.53230806487</v>
       </c>
       <c r="Q11">
         <f t="shared" si="0"/>
-        <v>1028684.0394578334</v>
+        <v>891002.60373663204</v>
       </c>
       <c r="R11">
         <f t="shared" si="0"/>
-        <v>1066616.1108864155</v>
+        <v>928934.67516521411</v>
       </c>
       <c r="S11">
         <f t="shared" si="0"/>
-        <v>1104548.1823149826</v>
+        <v>966866.74659378128</v>
       </c>
       <c r="T11">
         <f t="shared" si="0"/>
-        <v>1142480.2537435498</v>
+        <v>1004798.8180223485</v>
       </c>
       <c r="U11">
         <f t="shared" si="0"/>
-        <v>1180412.325172117</v>
+        <v>1042730.8894509156</v>
       </c>
       <c r="V11">
         <f t="shared" si="0"/>
-        <v>1218344.3966006991</v>
+        <v>1080662.9608794977</v>
       </c>
       <c r="W11">
         <f t="shared" si="0"/>
-        <v>1256276.4680292662</v>
+        <v>1118595.0323080649</v>
       </c>
       <c r="X11">
         <f t="shared" si="0"/>
-        <v>1294208.5394578334</v>
+        <v>1156527.103736632</v>
       </c>
       <c r="Y11">
         <f t="shared" si="0"/>
-        <v>1332140.6108864155</v>
+        <v>1194459.1751652141</v>
       </c>
       <c r="Z11">
         <f t="shared" si="0"/>
-        <v>1370072.6823149826</v>
+        <v>1232391.2465937813</v>
       </c>
       <c r="AA11">
         <f t="shared" si="0"/>
-        <v>1408004.7537435498</v>
+        <v>1270323.3180223485</v>
       </c>
       <c r="AB11">
         <f t="shared" si="0"/>
-        <v>1445936.825172117</v>
+        <v>1308255.3894509156</v>
       </c>
       <c r="AC11">
         <f t="shared" si="0"/>
-        <v>1483868.8966006991</v>
+        <v>1346187.4608794977</v>
       </c>
       <c r="AD11">
         <f t="shared" si="0"/>
-        <v>1521800.9680292662</v>
+        <v>1384119.5323080649</v>
       </c>
       <c r="AE11">
         <f t="shared" si="0"/>
-        <v>1559733.0394578334</v>
+        <v>1422051.603736632</v>
       </c>
       <c r="AF11">
         <f t="shared" si="0"/>
-        <v>1597665.1108864155</v>
+        <v>1459983.6751652141</v>
       </c>
     </row>
   </sheetData>
@@ -2441,7 +2432,7 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
   </cols>
@@ -2555,115 +2546,115 @@
       </c>
       <c r="D2" s="2">
         <f>Calculations!E11</f>
-        <v>251762.11802742296</v>
+        <v>240829.9902198707</v>
       </c>
       <c r="E2" s="2">
         <f>Calculations!F11</f>
-        <v>364830.05288038554</v>
+        <v>343757.9804397414</v>
       </c>
       <c r="F2" s="2">
         <f>Calculations!G11</f>
-        <v>479244.6991299307</v>
+        <v>446685.9706596121</v>
       </c>
       <c r="G2" s="2">
         <f>Calculations!H11</f>
-        <v>595164.49341096531</v>
+        <v>549613.9608794977</v>
       </c>
       <c r="H2" s="2">
         <f>Calculations!I11</f>
-        <v>647672.73524960212</v>
+        <v>587546.03230806487</v>
       </c>
       <c r="I2" s="2">
         <f>Calculations!J11</f>
-        <v>702002.99838949763</v>
+        <v>625478.10373663204</v>
       </c>
       <c r="J2" s="2">
         <f>Calculations!K11</f>
-        <v>758234.50114811282</v>
+        <v>663410.17516521411</v>
       </c>
       <c r="K2" s="2">
         <f>Calculations!L11</f>
-        <v>816525.68016030989</v>
+        <v>701342.24659378128</v>
       </c>
       <c r="L2" s="2">
         <f>Calculations!M11</f>
-        <v>876955.75374354981</v>
+        <v>739274.31802234845</v>
       </c>
       <c r="M2" s="2">
         <f>Calculations!N11</f>
-        <v>914887.82517211698</v>
+        <v>777206.38945091562</v>
       </c>
       <c r="N2" s="2">
         <f>Calculations!O11</f>
-        <v>952819.89660069905</v>
+        <v>815138.4608794977</v>
       </c>
       <c r="O2" s="2">
         <f>Calculations!P11</f>
-        <v>990751.96802926622</v>
+        <v>853070.53230806487</v>
       </c>
       <c r="P2" s="2">
         <f>Calculations!Q11</f>
-        <v>1028684.0394578334</v>
+        <v>891002.60373663204</v>
       </c>
       <c r="Q2" s="2">
         <f>Calculations!R11</f>
-        <v>1066616.1108864155</v>
+        <v>928934.67516521411</v>
       </c>
       <c r="R2" s="2">
         <f>Calculations!S11</f>
-        <v>1104548.1823149826</v>
+        <v>966866.74659378128</v>
       </c>
       <c r="S2" s="2">
         <f>Calculations!T11</f>
-        <v>1142480.2537435498</v>
+        <v>1004798.8180223485</v>
       </c>
       <c r="T2" s="2">
         <f>Calculations!U11</f>
-        <v>1180412.325172117</v>
+        <v>1042730.8894509156</v>
       </c>
       <c r="U2" s="2">
         <f>Calculations!V11</f>
-        <v>1218344.3966006991</v>
+        <v>1080662.9608794977</v>
       </c>
       <c r="V2" s="2">
         <f>Calculations!W11</f>
-        <v>1256276.4680292662</v>
+        <v>1118595.0323080649</v>
       </c>
       <c r="W2" s="2">
         <f>Calculations!X11</f>
-        <v>1294208.5394578334</v>
+        <v>1156527.103736632</v>
       </c>
       <c r="X2" s="2">
         <f>Calculations!Y11</f>
-        <v>1332140.6108864155</v>
+        <v>1194459.1751652141</v>
       </c>
       <c r="Y2" s="2">
         <f>Calculations!Z11</f>
-        <v>1370072.6823149826</v>
+        <v>1232391.2465937813</v>
       </c>
       <c r="Z2" s="2">
         <f>Calculations!AA11</f>
-        <v>1408004.7537435498</v>
+        <v>1270323.3180223485</v>
       </c>
       <c r="AA2" s="2">
         <f>Calculations!AB11</f>
-        <v>1445936.825172117</v>
+        <v>1308255.3894509156</v>
       </c>
       <c r="AB2" s="2">
         <f>Calculations!AC11</f>
-        <v>1483868.8966006991</v>
+        <v>1346187.4608794977</v>
       </c>
       <c r="AC2" s="2">
         <f>Calculations!AD11</f>
-        <v>1521800.9680292662</v>
+        <v>1384119.5323080649</v>
       </c>
       <c r="AD2" s="2">
         <f>Calculations!AE11</f>
-        <v>1559733.0394578334</v>
+        <v>1422051.603736632</v>
       </c>
       <c r="AE2" s="2">
         <f>Calculations!AF11</f>
-        <v>1597665.1108864155</v>
+        <v>1459983.6751652141</v>
       </c>
       <c r="AF2" s="2"/>
     </row>
